--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_3_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_3_8.xlsx
@@ -513,1321 +513,1321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_0</t>
+          <t>model_3_8_6</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998503930820583</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6607815442994873</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9992550665227333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9996526749545723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9996266845319626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004318031535288324</v>
+        <v>8.881312917257012e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2013747287781163</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0001039341232541265</v>
       </c>
       <c r="J2" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0003988724736102616</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0002514031686453427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.003193392554605309</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.009424071793687171</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000872853906518</v>
+        <v>1.00017952830153</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.009825274040462429</v>
       </c>
       <c r="P2" t="n">
-        <v>103.4950814733877</v>
+        <v>106.6579521357052</v>
       </c>
       <c r="Q2" t="n">
-        <v>157.1256177675886</v>
+        <v>160.288488429906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_22</t>
+          <t>model_3_8_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998639875425906</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6607744807519829</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9994958212056584</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9996779675799113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.999673190645017</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004318031535288324</v>
+        <v>8.074287015044594e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2013789220050443</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004085739463202047</v>
+        <v>7.034370524666013e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0003698261028810267</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0002200843908707876</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.002974160752038151</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.008985703653606986</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000163214948891</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.009368243661111882</v>
       </c>
       <c r="P3" t="n">
-        <v>103.4950814733877</v>
+        <v>106.8484817902206</v>
       </c>
       <c r="Q3" t="n">
-        <v>157.1256177675886</v>
+        <v>160.4790180844214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_21</t>
+          <t>model_3_8_7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998356194608629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6607605963955336</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9990051414724567</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.999626690532095</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9995786389772685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004318031535288324</v>
+        <v>9.758338890138781e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2013871643588055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0001388040032802646</v>
       </c>
       <c r="J4" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.000428713312920172</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0002837586581002183</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.003386975715947249</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.009878430487754004</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000197256646965</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01029897572478785</v>
       </c>
       <c r="P4" t="n">
-        <v>103.4950814733877</v>
+        <v>106.4696065494253</v>
       </c>
       <c r="Q4" t="n">
-        <v>157.1256177675886</v>
+        <v>160.1001428436261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_20</t>
+          <t>model_3_8_4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998754504639977</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6607385134667616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9997128790961687</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9997017318022164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9997159374867648</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004318031535288324</v>
+        <v>7.393798483074052e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2014002737392574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004085739463202047</v>
+        <v>4.00594956708552e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.000342534969520315</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0001912972325955851</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.002725354244622358</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.008598719953036064</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000149459443203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.008964785263240961</v>
       </c>
       <c r="P5" t="n">
-        <v>103.4950814733877</v>
+        <v>107.0245677178843</v>
       </c>
       <c r="Q5" t="n">
-        <v>157.1256177675886</v>
+        <v>160.6551040120851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_19</t>
+          <t>model_3_8_8</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998203546742486</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6607207591075833</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9987552237483436</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9996007503789479</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9995306323682296</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001066452256400505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.201410813493814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0001736728611501918</v>
       </c>
       <c r="J6" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0004585033127713264</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0003160879202434491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.003558177019339906</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01032691752848111</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000215574390902</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01076655578733487</v>
       </c>
       <c r="P6" t="n">
-        <v>103.4950814733877</v>
+        <v>106.2920057613366</v>
       </c>
       <c r="Q6" t="n">
-        <v>157.1256177675886</v>
+        <v>159.9225420555374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_18</t>
+          <t>model_3_8_9</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998050874831015</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6606668985803859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.998511769320932</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9995753391448264</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9994837465252802</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001157084898132606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2014427874294121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0002076399511488895</v>
       </c>
       <c r="J7" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0004876858953259749</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0003476624208770489</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.003709914208760648</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01075678808070795</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000233895020278</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01121472681892472</v>
       </c>
       <c r="P7" t="n">
-        <v>103.4950814733877</v>
+        <v>106.1288730972822</v>
       </c>
       <c r="Q7" t="n">
-        <v>157.1256177675886</v>
+        <v>159.759409391483</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_17</t>
+          <t>model_3_8_3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998834297024806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.660661051959585</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9998862431758471</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9997226005021437</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9997516899879136</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004318031535288324</v>
+        <v>6.920116418217915e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2014462582360803</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004085739463202047</v>
+        <v>1.587150550125556e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0003185690906682681</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0001672202980847618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.002441975595554123</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.008318723711133767</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000139884357023</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.008672869001648759</v>
       </c>
       <c r="P8" t="n">
-        <v>103.4950814733877</v>
+        <v>107.1569857440805</v>
       </c>
       <c r="Q8" t="n">
-        <v>157.1256177675886</v>
+        <v>160.7875220382814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_16</t>
+          <t>model_3_8_10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997901240986879</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6606036089855226</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9982781716895222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9995507877717353</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9994386136635039</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001245914011857273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.201480358866891</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0002402318076780204</v>
       </c>
       <c r="J9" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.000515881002601669</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0003780564051398447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.003844897797192499</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01116205183582872</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000251851081575</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01163724349111261</v>
       </c>
       <c r="P9" t="n">
-        <v>103.4950814733877</v>
+        <v>105.9809419306856</v>
       </c>
       <c r="Q9" t="n">
-        <v>157.1256177675886</v>
+        <v>159.6114782248865</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_15</t>
+          <t>model_3_8_11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997756895287881</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6605348516766825</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9980568631509246</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9995273097826408</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9993956697951208</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001331603854191479</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2015211761755796</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0002711090734067535</v>
       </c>
       <c r="J10" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0005428434221243639</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0004069762477655587</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.0039650659082617</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01153951408938643</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000269172565454</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01203077509425885</v>
       </c>
       <c r="P10" t="n">
-        <v>103.4950814733877</v>
+        <v>105.8479125017106</v>
       </c>
       <c r="Q10" t="n">
-        <v>157.1256177675886</v>
+        <v>159.4784487959114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_14</t>
+          <t>model_3_8_2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998860302335456</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6605307305434314</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9999866333522109</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9997387204719119</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9997758340849232</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004318031535288324</v>
+        <v>6.765737660487982e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2015236226583012</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0004085739463202047</v>
+        <v>1.864932723793079e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0003000567135718911</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0001509608526238227</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.002118911233609981</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.008225410421667712</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000136763719745</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.008575583172264997</v>
       </c>
       <c r="P11" t="n">
-        <v>103.4950814733877</v>
+        <v>107.2021083371389</v>
       </c>
       <c r="Q11" t="n">
-        <v>157.1256177675886</v>
+        <v>160.8326446313397</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_13</t>
+          <t>model_3_8_12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997619441461659</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6604652686100371</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9978490324838236</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9995051269819895</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9993552264418116</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001413202383133088</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2015624836897723</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0003001058883300299</v>
       </c>
       <c r="J12" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0005683184308629636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0004342121595964967</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004072299567066461</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01188781890479952</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000285667024601</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01239390796675444</v>
       </c>
       <c r="P12" t="n">
-        <v>103.4950814733877</v>
+        <v>105.7289640982732</v>
       </c>
       <c r="Q12" t="n">
-        <v>157.1256177675886</v>
+        <v>159.359500392474</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_23</t>
+          <t>model_3_8_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997489533046181</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6603951070197652</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.997655166300934</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9994842621818709</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9993173550805944</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001490321630312638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2016041346405806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0003271543595857233</v>
       </c>
       <c r="J13" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0005922798311253719</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0004597160056090178</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004168106133435748</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01220787299373908</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000301256034458</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01272758742086345</v>
       </c>
       <c r="P13" t="n">
-        <v>103.4950814733877</v>
+        <v>105.6226968320857</v>
       </c>
       <c r="Q13" t="n">
-        <v>157.1256177675886</v>
+        <v>159.2532331262865</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_12</t>
+          <t>model_3_8_1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998807146195881</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6603409761525874</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9999730295469598</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9997477594031159</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9997821320079278</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004318031535288324</v>
+        <v>7.081295467263818e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2016362690616691</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0004085739463202047</v>
+        <v>3.762953976486028e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0002896762906925402</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0001467196198467287</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.002008508962519431</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.008415043355362953</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000143142456494</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.008773289172541932</v>
       </c>
       <c r="P14" t="n">
-        <v>103.4950814733877</v>
+        <v>107.1109371968007</v>
       </c>
       <c r="Q14" t="n">
-        <v>157.1256177675886</v>
+        <v>160.7414734910016</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_10</t>
+          <t>model_3_8_14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.999736767770807</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.660326757320989</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9974752433323592</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9994647710504639</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9992820999782508</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001562660222891627</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2016447099743274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0003522574547784988</v>
       </c>
       <c r="J15" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0006146636928713743</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0004834579750663638</v>
       </c>
       <c r="L15" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004253898034259553</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01250064087513767</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000315878675032</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01303281903708625</v>
       </c>
       <c r="P15" t="n">
-        <v>103.4950814733877</v>
+        <v>105.5279014639085</v>
       </c>
       <c r="Q15" t="n">
-        <v>157.1256177675886</v>
+        <v>159.1584377581094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_9</t>
+          <t>model_3_8_15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997253969949434</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.660260264618286</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9973090090833971</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9994466217008954</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9992494001191421</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001630162060337582</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.201684182914987</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0003754506813523274</v>
       </c>
       <c r="J16" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0006355066353891126</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.000505479157947995</v>
       </c>
       <c r="L16" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004330667272375986</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01276777999629373</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000329523606068</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01331133082368413</v>
       </c>
       <c r="P16" t="n">
-        <v>103.4950814733877</v>
+        <v>105.4433218771594</v>
       </c>
       <c r="Q16" t="n">
-        <v>157.1256177675886</v>
+        <v>159.0738581713603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_8</t>
+          <t>model_3_8_0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9998780745265149</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6602542741951465</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9999790187185392</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9997477524532006</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.999782746493888</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004318031535288324</v>
+        <v>7.238022796696792e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2016877390889355</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0004085739463202047</v>
+        <v>2.927336681622297e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0002896842720631587</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0001463058043723905</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.001935118726602232</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.00850765701982443</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000146310568182</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.008869845592436251</v>
       </c>
       <c r="P17" t="n">
-        <v>103.4950814733877</v>
+        <v>107.0671547804971</v>
       </c>
       <c r="Q17" t="n">
-        <v>157.1256177675886</v>
+        <v>160.697691074698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_7</t>
+          <t>model_3_8_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997148312107815</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6601965705857187</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.997155745475324</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9994298069590426</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9992191851361112</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001692885119303539</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.201721994444158</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0003968342266190662</v>
       </c>
       <c r="J18" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0006548168975318135</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0005258269418597422</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004399525311834985</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01301109188078979</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000342202547062</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01356500099882823</v>
       </c>
       <c r="P18" t="n">
-        <v>103.4950814733877</v>
+        <v>105.3678122548321</v>
       </c>
       <c r="Q18" t="n">
-        <v>157.1256177675886</v>
+        <v>158.9983485490329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_6</t>
+          <t>model_3_8_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9997050799808076</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6601371349505908</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9970152193571457</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.999414315010178</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.999191420865433</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001750772632740779</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2017572780046556</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004164406201198215</v>
       </c>
       <c r="J19" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0006726080474821153</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0005445243338009684</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004461219226767698</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01323167651033224</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000353904023031</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01379497637272343</v>
       </c>
       <c r="P19" t="n">
-        <v>103.4950814733877</v>
+        <v>105.3005663541037</v>
       </c>
       <c r="Q19" t="n">
-        <v>157.1256177675886</v>
+        <v>158.9311026483045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_5</t>
+          <t>model_3_8_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.999696082745226</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6600813021255267</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9968865029917477</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9994000275839675</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9991659060273967</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001804184109756444</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2017904227814662</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004343993009877781</v>
       </c>
       <c r="J20" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0006890159083868387</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0005617068822860508</v>
       </c>
       <c r="L20" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004516572666271365</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01343199207026435</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000364700705729</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01400381978075223</v>
       </c>
       <c r="P20" t="n">
-        <v>103.4950814733877</v>
+        <v>105.2404637982743</v>
       </c>
       <c r="Q20" t="n">
-        <v>157.1256177675886</v>
+        <v>158.8710000924751</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_4</t>
+          <t>model_3_8_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.999687816853664</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6600293352373876</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9967687765830611</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9993869270592648</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9991425373191294</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.000185325401274762</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2018212725711182</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004508246482759623</v>
       </c>
       <c r="J21" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0007040607165932377</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0005774441549376239</v>
       </c>
       <c r="L21" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004566320978653815</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01361342724205635</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000374619775603</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01419297902343</v>
       </c>
       <c r="P21" t="n">
-        <v>103.4950814733877</v>
+        <v>105.1867947043498</v>
       </c>
       <c r="Q21" t="n">
-        <v>157.1256177675886</v>
+        <v>158.8173309985506</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_3</t>
+          <t>model_3_8_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9996802329489894</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6599810704311191</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.996661301257403</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.999374924307459</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9991211724008231</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.000189827534697203</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2018499246450502</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004658197506369286</v>
       </c>
       <c r="J22" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0007178448285250496</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0005918320081607653</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.00461099776288885</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.0137777913577323</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000383720461213</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.0143643404597909</v>
       </c>
       <c r="P22" t="n">
-        <v>103.4950814733877</v>
+        <v>105.1387892202878</v>
       </c>
       <c r="Q22" t="n">
-        <v>157.1256177675886</v>
+        <v>158.7693255144886</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_2</t>
+          <t>model_3_8_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9996733007531133</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6599366712738506</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9965635069630648</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9993639533862827</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9991016871090369</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001939427856245836</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2018762819027486</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004794641424537522</v>
       </c>
       <c r="J23" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.000730443973115995</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0006049540577848737</v>
       </c>
       <c r="L23" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004651124007155168</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01392633424934873</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000392039096264</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01451920712982962</v>
       </c>
       <c r="P23" t="n">
-        <v>103.4950814733877</v>
+        <v>105.0958947237183</v>
       </c>
       <c r="Q23" t="n">
-        <v>157.1256177675886</v>
+        <v>158.7264310179191</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_1</t>
+          <t>model_3_8_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9996669727857582</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6598955688791217</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9964745036708698</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9993539485733222</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9990839362169267</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0001976993404005184</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2019006820597906</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0004918820017973312</v>
       </c>
       <c r="J24" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0007419336268167753</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0006169081044420837</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004687118009810976</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01406055974705554</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000872853906518</v>
+        <v>1.00039963265709</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01465914688485888</v>
       </c>
       <c r="P24" t="n">
-        <v>103.4950814733877</v>
+        <v>105.0575263283178</v>
       </c>
       <c r="Q24" t="n">
-        <v>157.1256177675886</v>
+        <v>158.6880626225186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_3_8_11</t>
+          <t>model_3_8_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9996612048828034</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.659858015096336</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9963936133532938</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9993448461509908</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9990677960334309</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0002011234167548907</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2019229756074911</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.0005031679279821233</v>
       </c>
       <c r="J25" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0007523869637094667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0006277774458457951</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004719593794340835</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01418179878417723</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000406554140636</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01478554731879025</v>
       </c>
       <c r="P25" t="n">
-        <v>103.4950814733877</v>
+        <v>105.0231836492571</v>
       </c>
       <c r="Q25" t="n">
-        <v>157.1256177675886</v>
+        <v>158.653719943458</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9992726217445683</v>
+        <v>0.9996559471445701</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6763393751765534</v>
+        <v>0.6598237736344303</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9990381330239143</v>
+        <v>0.9963201197193274</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999999999994024</v>
+        <v>0.9993365422787921</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9996306262922494</v>
+        <v>0.9990531001875134</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004318031535288324</v>
+        <v>0.0002042446372926971</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1921389283061898</v>
+        <v>0.2019433028184325</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0004085739463202047</v>
+        <v>0.000513421858895619</v>
       </c>
       <c r="J26" t="n">
-        <v>3.845905882461293e-13</v>
+        <v>0.0007619232355334515</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0002042869733718677</v>
+        <v>0.0006376741218367612</v>
       </c>
       <c r="L26" t="n">
-        <v>0.009042760443226225</v>
+        <v>0.004748696148080218</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02077987376113802</v>
+        <v>0.01429141830934554</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000872853906518</v>
+        <v>1.000412863426516</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02166451600741838</v>
+        <v>0.01489983357408868</v>
       </c>
       <c r="P26" t="n">
-        <v>103.4950814733877</v>
+        <v>104.9923841603475</v>
       </c>
       <c r="Q26" t="n">
-        <v>157.1256177675886</v>
+        <v>158.6229204545483</v>
       </c>
     </row>
   </sheetData>
